--- a/artfynd/A 35678-2026 artfynd.xlsx
+++ b/artfynd/A 35678-2026 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>137370916</v>
       </c>
       <c r="B4" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137370913</v>
       </c>
       <c r="B5" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137370908</v>
       </c>
       <c r="B6" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137370921</v>
       </c>
       <c r="B9" t="n">
-        <v>92558</v>
+        <v>92560</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35678-2026 artfynd.xlsx
+++ b/artfynd/A 35678-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370909</v>
       </c>
       <c r="B2" t="n">
-        <v>89523</v>
+        <v>89528</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137370918</v>
       </c>
       <c r="B3" t="n">
-        <v>79595</v>
+        <v>79600</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137370916</v>
       </c>
       <c r="B4" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137370913</v>
       </c>
       <c r="B5" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137370908</v>
       </c>
       <c r="B6" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137370911</v>
       </c>
       <c r="B7" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137370917</v>
       </c>
       <c r="B8" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137370921</v>
       </c>
       <c r="B9" t="n">
-        <v>92560</v>
+        <v>92565</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137370915</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137370919</v>
       </c>
       <c r="B11" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137370907</v>
       </c>
       <c r="B12" t="n">
-        <v>83505</v>
+        <v>83510</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137370914</v>
       </c>
       <c r="B13" t="n">
-        <v>83505</v>
+        <v>83510</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35678-2026 artfynd.xlsx
+++ b/artfynd/A 35678-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370909</v>
       </c>
       <c r="B2" t="n">
-        <v>89528</v>
+        <v>89539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137370918</v>
       </c>
       <c r="B3" t="n">
-        <v>79600</v>
+        <v>79611</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137370916</v>
       </c>
       <c r="B4" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137370913</v>
       </c>
       <c r="B5" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137370908</v>
       </c>
       <c r="B6" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137370911</v>
       </c>
       <c r="B7" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137370917</v>
       </c>
       <c r="B8" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137370921</v>
       </c>
       <c r="B9" t="n">
-        <v>92565</v>
+        <v>92577</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137370915</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137370919</v>
       </c>
       <c r="B11" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137370907</v>
       </c>
       <c r="B12" t="n">
-        <v>83510</v>
+        <v>83521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137370914</v>
       </c>
       <c r="B13" t="n">
-        <v>83510</v>
+        <v>83521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35678-2026 artfynd.xlsx
+++ b/artfynd/A 35678-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370909</v>
       </c>
       <c r="B2" t="n">
-        <v>89539</v>
+        <v>89540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137370918</v>
       </c>
       <c r="B3" t="n">
-        <v>79611</v>
+        <v>79612</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137370916</v>
       </c>
       <c r="B4" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137370913</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137370908</v>
       </c>
       <c r="B6" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137370911</v>
       </c>
       <c r="B7" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137370917</v>
       </c>
       <c r="B8" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137370921</v>
       </c>
       <c r="B9" t="n">
-        <v>92577</v>
+        <v>92578</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137370915</v>
       </c>
       <c r="B10" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137370919</v>
       </c>
       <c r="B11" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137370907</v>
       </c>
       <c r="B12" t="n">
-        <v>83521</v>
+        <v>83522</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137370914</v>
       </c>
       <c r="B13" t="n">
-        <v>83521</v>
+        <v>83522</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35678-2026 artfynd.xlsx
+++ b/artfynd/A 35678-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370909</v>
       </c>
       <c r="B2" t="n">
-        <v>89540</v>
+        <v>89543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137370918</v>
       </c>
       <c r="B3" t="n">
-        <v>79612</v>
+        <v>79614</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137370916</v>
       </c>
       <c r="B4" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137370913</v>
       </c>
       <c r="B5" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137370908</v>
       </c>
       <c r="B6" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137370911</v>
       </c>
       <c r="B7" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137370917</v>
       </c>
       <c r="B8" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137370921</v>
       </c>
       <c r="B9" t="n">
-        <v>92578</v>
+        <v>92581</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137370915</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137370919</v>
       </c>
       <c r="B11" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137370907</v>
       </c>
       <c r="B12" t="n">
-        <v>83522</v>
+        <v>83524</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137370914</v>
       </c>
       <c r="B13" t="n">
-        <v>83522</v>
+        <v>83524</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35678-2026 artfynd.xlsx
+++ b/artfynd/A 35678-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370909</v>
       </c>
       <c r="B2" t="n">
-        <v>89543</v>
+        <v>89547</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137370918</v>
       </c>
       <c r="B3" t="n">
-        <v>79614</v>
+        <v>79618</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137370916</v>
       </c>
       <c r="B4" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137370913</v>
       </c>
       <c r="B5" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137370908</v>
       </c>
       <c r="B6" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137370911</v>
       </c>
       <c r="B7" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137370917</v>
       </c>
       <c r="B8" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137370921</v>
       </c>
       <c r="B9" t="n">
-        <v>92581</v>
+        <v>92585</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137370915</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137370919</v>
       </c>
       <c r="B11" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137370907</v>
       </c>
       <c r="B12" t="n">
-        <v>83524</v>
+        <v>83528</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137370914</v>
       </c>
       <c r="B13" t="n">
-        <v>83524</v>
+        <v>83528</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
